--- a/data/nzd0484/nzd0484.xlsx
+++ b/data/nzd0484/nzd0484.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E569"/>
+  <dimension ref="A1:E572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12381,6 +12381,69 @@
         <v>337.78</v>
       </c>
       <c r="E569" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>328.99</v>
+      </c>
+      <c r="C570" t="n">
+        <v>335.81</v>
+      </c>
+      <c r="D570" t="n">
+        <v>337.41</v>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>329.68</v>
+      </c>
+      <c r="C571" t="n">
+        <v>336.29</v>
+      </c>
+      <c r="D571" t="n">
+        <v>338.05</v>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>329.56</v>
+      </c>
+      <c r="C572" t="n">
+        <v>336.48</v>
+      </c>
+      <c r="D572" t="n">
+        <v>338.31</v>
+      </c>
+      <c r="E572" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12397,7 +12460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B715"/>
+  <dimension ref="A1:B718"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19550,6 +19613,36 @@
       </c>
       <c r="B715" t="n">
         <v>-0.71</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>0.27</v>
       </c>
     </row>
   </sheetData>
@@ -19718,28 +19811,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3283368980875597</v>
+        <v>-0.330235578132439</v>
       </c>
       <c r="J2" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="K2" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2817726672670322</v>
+        <v>0.2862518896442278</v>
       </c>
       <c r="M2" t="n">
-        <v>2.86952244360916</v>
+        <v>2.862805237505535</v>
       </c>
       <c r="N2" t="n">
-        <v>12.65982740733252</v>
+        <v>12.60808013815283</v>
       </c>
       <c r="O2" t="n">
-        <v>3.558065121288889</v>
+        <v>3.550785847971239</v>
       </c>
       <c r="P2" t="n">
-        <v>339.8924278935469</v>
+        <v>339.915552924458</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19796,28 +19889,28 @@
         <v>0.0818</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.390772196261729</v>
+        <v>-0.3933107763015077</v>
       </c>
       <c r="J3" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="K3" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="L3" t="n">
-        <v>0.499840961434436</v>
+        <v>0.5050715435533262</v>
       </c>
       <c r="M3" t="n">
-        <v>2.026331624182521</v>
+        <v>2.027383121329398</v>
       </c>
       <c r="N3" t="n">
-        <v>7.039615314098498</v>
+        <v>7.028551743657486</v>
       </c>
       <c r="O3" t="n">
-        <v>2.653227339316874</v>
+        <v>2.651141592532825</v>
       </c>
       <c r="P3" t="n">
-        <v>348.9131233116815</v>
+        <v>348.9440431405906</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19874,28 +19967,28 @@
         <v>0.0785</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3060175533634437</v>
+        <v>-0.3114005699137574</v>
       </c>
       <c r="J4" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="K4" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="L4" t="n">
-        <v>0.269026685755151</v>
+        <v>0.2763049219678925</v>
       </c>
       <c r="M4" t="n">
-        <v>2.74975967528972</v>
+        <v>2.758599423566367</v>
       </c>
       <c r="N4" t="n">
-        <v>11.72260619643865</v>
+        <v>11.77634266797422</v>
       </c>
       <c r="O4" t="n">
-        <v>3.423829171620373</v>
+        <v>3.431667622013272</v>
       </c>
       <c r="P4" t="n">
-        <v>350.855845458975</v>
+        <v>350.9214136761464</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19933,7 +20026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E569"/>
+  <dimension ref="A1:E572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35299,6 +35392,87 @@
         </is>
       </c>
     </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>-45.359902240222084,170.86294201319652</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>-45.360507962305356,170.86266279174393</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>-45.36110701823813,170.86237795543812</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>-45.359904814046885,170.86295002776598</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>-45.36050962558459,170.86266844587593</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>-45.361109063664244,170.86238559174203</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>-45.359904366425226,170.86294863392777</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>-45.36051028396587,170.86267068396998</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>-45.36110989461846,170.86238869399065</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0484/nzd0484.xlsx
+++ b/data/nzd0484/nzd0484.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E572"/>
+  <dimension ref="A1:E574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12444,6 +12444,48 @@
         <v>338.31</v>
       </c>
       <c r="E572" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>328.39</v>
+      </c>
+      <c r="C573" t="n">
+        <v>336.54</v>
+      </c>
+      <c r="D573" t="n">
+        <v>338.71</v>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="C574" t="n">
+        <v>336.7</v>
+      </c>
+      <c r="D574" t="n">
+        <v>339.06</v>
+      </c>
+      <c r="E574" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12460,7 +12502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B718"/>
+  <dimension ref="A1:B720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19643,6 +19685,26 @@
       </c>
       <c r="B718" t="n">
         <v>0.27</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -19811,28 +19873,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.330235578132439</v>
+        <v>-0.3321876092198076</v>
       </c>
       <c r="J2" t="n">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="K2" t="n">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2862518896442278</v>
+        <v>0.289894114652404</v>
       </c>
       <c r="M2" t="n">
-        <v>2.862805237505535</v>
+        <v>2.861387543801078</v>
       </c>
       <c r="N2" t="n">
-        <v>12.60808013815283</v>
+        <v>12.58680571559826</v>
       </c>
       <c r="O2" t="n">
-        <v>3.550785847971239</v>
+        <v>3.547788848789941</v>
       </c>
       <c r="P2" t="n">
-        <v>339.915552924458</v>
+        <v>339.9394148953411</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19889,28 +19951,28 @@
         <v>0.0818</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3933107763015077</v>
+        <v>-0.394618639885363</v>
       </c>
       <c r="J3" t="n">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="K3" t="n">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5050715435533262</v>
+        <v>0.5083110615967033</v>
       </c>
       <c r="M3" t="n">
-        <v>2.027383121329398</v>
+        <v>2.026319828011392</v>
       </c>
       <c r="N3" t="n">
-        <v>7.028551743657486</v>
+        <v>7.014246517379032</v>
       </c>
       <c r="O3" t="n">
-        <v>2.651141592532825</v>
+        <v>2.64844228130028</v>
       </c>
       <c r="P3" t="n">
-        <v>348.9440431405906</v>
+        <v>348.9600303378904</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19967,28 +20029,28 @@
         <v>0.0785</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3114005699137574</v>
+        <v>-0.3141705492028469</v>
       </c>
       <c r="J4" t="n">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="K4" t="n">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2763049219678925</v>
+        <v>0.2806430337342101</v>
       </c>
       <c r="M4" t="n">
-        <v>2.758599423566367</v>
+        <v>2.760946148335408</v>
       </c>
       <c r="N4" t="n">
-        <v>11.77634266797422</v>
+        <v>11.78110663143538</v>
       </c>
       <c r="O4" t="n">
-        <v>3.431667622013272</v>
+        <v>3.432361669672265</v>
       </c>
       <c r="P4" t="n">
-        <v>350.9214136761464</v>
+        <v>350.9552736788526</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20026,7 +20088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E572"/>
+  <dimension ref="A1:E574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35473,6 +35535,60 @@
         </is>
       </c>
     </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>-45.359900002113086,170.86293504400626</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>-45.36051049187574,170.8626713907365</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>-45.361111173009405,170.86239346668103</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>-45.359900412433106,170.8629363216911</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>-45.360511046302044,170.86267327544732</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>-45.361112291601316,170.86239764278528</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0484/nzd0484.xlsx
+++ b/data/nzd0484/nzd0484.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E574"/>
+  <dimension ref="A1:E576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12486,6 +12486,48 @@
         <v>339.06</v>
       </c>
       <c r="E574" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>329.3</v>
+      </c>
+      <c r="C575" t="n">
+        <v>337.36</v>
+      </c>
+      <c r="D575" t="n">
+        <v>339.39</v>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>331.28</v>
+      </c>
+      <c r="C576" t="n">
+        <v>338.97</v>
+      </c>
+      <c r="D576" t="n">
+        <v>341.16</v>
+      </c>
+      <c r="E576" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12502,7 +12544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B720"/>
+  <dimension ref="A1:B723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19705,6 +19747,36 @@
       </c>
       <c r="B720" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -19873,28 +19945,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3321876092198076</v>
+        <v>-0.3326903339421085</v>
       </c>
       <c r="J2" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K2" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="L2" t="n">
-        <v>0.289894114652404</v>
+        <v>0.292040714018683</v>
       </c>
       <c r="M2" t="n">
-        <v>2.861387543801078</v>
+        <v>2.854832875574625</v>
       </c>
       <c r="N2" t="n">
-        <v>12.58680571559826</v>
+        <v>12.54806638203939</v>
       </c>
       <c r="O2" t="n">
-        <v>3.547788848789941</v>
+        <v>3.542324996670886</v>
       </c>
       <c r="P2" t="n">
-        <v>339.9394148953411</v>
+        <v>339.9455664260763</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19951,28 +20023,28 @@
         <v>0.0818</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.394618639885363</v>
+        <v>-0.394710785683202</v>
       </c>
       <c r="J3" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K3" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5083110615967033</v>
+        <v>0.51028721874849</v>
       </c>
       <c r="M3" t="n">
-        <v>2.026319828011392</v>
+        <v>2.022124513920884</v>
       </c>
       <c r="N3" t="n">
-        <v>7.014246517379032</v>
+        <v>6.992239521956554</v>
       </c>
       <c r="O3" t="n">
-        <v>2.64844228130028</v>
+        <v>2.644284311861445</v>
       </c>
       <c r="P3" t="n">
-        <v>348.9600303378904</v>
+        <v>348.9611507427367</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20029,28 +20101,28 @@
         <v>0.0785</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3141705492028469</v>
+        <v>-0.3158220388595998</v>
       </c>
       <c r="J4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2806430337342101</v>
+        <v>0.2840140374092278</v>
       </c>
       <c r="M4" t="n">
-        <v>2.760946148335408</v>
+        <v>2.75843222385623</v>
       </c>
       <c r="N4" t="n">
-        <v>11.78110663143538</v>
+        <v>11.75929075190737</v>
       </c>
       <c r="O4" t="n">
-        <v>3.432361669672265</v>
+        <v>3.429182227865322</v>
       </c>
       <c r="P4" t="n">
-        <v>350.9552736788526</v>
+        <v>350.9755089069488</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20088,7 +20160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E574"/>
+  <dimension ref="A1:E576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35589,6 +35661,60 @@
         </is>
       </c>
     </row>
+    <row r="575">
+      <c r="A575" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>-45.359903396578225,170.86294561394502</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>-45.360513333310216,170.8626810498798</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>-45.36111334627355,170.86240158025518</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>-45.35991078233421,170.86296861227777</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>-45.36051891222192,170.862700014786</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>-45.36111900314964,170.86242269941442</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
